--- a/thesis/tables/Performance_Report.xlsx
+++ b/thesis/tables/Performance_Report.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\URL-Phishing-Detection\thesis\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C5957B-DC3F-42F3-B8F3-91ABDF8B4579}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9285CF3F-473E-46AE-844C-04F7C26481CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Performance Summary" sheetId="1" r:id="rId1"/>
